--- a/examples/excel/charts/charts-stock.xlsx
+++ b/examples/excel/charts/charts-stock.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Stock Fundamentals" sheetId="2" r:id="Rbc3767f7510e4762"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Stock Styling" sheetId="3" r:id="Ra2674e21505c4601"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Stock Advanced" sheetId="4" r:id="R8fbb96f41f4b4949"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Stock Fundamentals" sheetId="2" r:id="R44e3d9c0e18042f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Stock Styling" sheetId="3" r:id="R07be1a2239c94a02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Stock Advanced" sheetId="4" r:id="Raf714b9f26414cc1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1386,7 +1386,7 @@
         <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
-        <c:numFmt formatCode="0,##0" sourceLinked="0"/>
+        <c:numFmt formatCode="$#,##0" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3968,6 +3968,26 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:dLbls>
+          <c:txPr>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:pPr>
+                <a:defRPr sz="800">
+                  <a:solidFill>
+                    <a:srgbClr val="666666"/>
+                  </a:solidFill>
+                </a:defRPr>
+              </a:pPr>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+        </c:dLbls>
         <c:hiLowLines/>
         <c:upDownBars>
           <c:gapWidth val="150"/>
@@ -3986,26 +4006,6 @@
             </c:spPr>
           </c:downBars>
         </c:upDownBars>
-        <c:dLbls>
-          <c:txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:pPr>
-                <a:defRPr sz="800" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="666666"/>
-                  </a:solidFill>
-                </a:defRPr>
-              </a:pPr>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-        </c:dLbls>
         <c:axId val="1"/>
         <c:axId val="2"/>
       </c:stockChart>
@@ -4078,7 +4078,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd43dbf6807e245d0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9d95a211d0be4d1a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4108,7 +4108,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R370b44470731455a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbd2141c1a1b745b6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4138,7 +4138,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb1b8a4cf04fa473a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd771ab9113ab441f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4168,7 +4168,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd46176d2c7bd4eea"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2c422a5aff0b447c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4203,7 +4203,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfadbad9a47fa4e0c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R212e6e8ebc6c4eaf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4233,7 +4233,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd87690107a3d449d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd0be36511ce04500"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4263,7 +4263,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra941371964914cc3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd0749429b18c4bb7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4293,7 +4293,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0636a4fa1020415e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb0779fb492464e8f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4328,7 +4328,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raaa3b433380742fc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rddab27ed5e03456b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4358,7 +4358,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3fac8eed08dd4bb9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R268c046df41c4d9a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4388,7 +4388,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0872f6c1aa664dd6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb80dce4db94d4cf3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4418,7 +4418,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3ede06f387dd4c11"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R427d717db4c64656"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4427,23 +4427,132 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd39151dd0b547a7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f26e4c6980545c1"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87ba56a7ce274583"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff1dd014f434426e"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf69556cfaaf245c3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4630384b26d64edf"/>
 </x:worksheet>
 </file>